--- a/public/template-import/TEMPLATE_IMPORT_PROJECT_KOBRA.xlsx
+++ b/public/template-import/TEMPLATE_IMPORT_PROJECT_KOBRA.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="14540"/>
+    <workbookView windowWidth="25820" windowHeight="13260"/>
   </bookViews>
   <sheets>
     <sheet name="import_data" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="68">
   <si>
     <t>MEMO INFORMATION</t>
   </si>
@@ -53,6 +53,12 @@
     <t>*MIN 1 VALUE</t>
   </si>
   <si>
+    <t>*REQUIRED/*OPTIONAL FOR PROCUREMENT</t>
+  </si>
+  <si>
+    <t>*REQUIRED (CAN USE FOR PROCUREMENT PROGRESSION STEPS)</t>
+  </si>
+  <si>
     <t>MEMO_NUMBER</t>
   </si>
   <si>
@@ -131,6 +137,9 @@
     <t>PROJECT_NUMBER</t>
   </si>
   <si>
+    <t>PROJECT_NAME</t>
+  </si>
+  <si>
     <t>DIVISION_CODE_INITIATION</t>
   </si>
   <si>
@@ -173,70 +182,55 @@
     <t>PROJECT_FEATURES</t>
   </si>
   <si>
-    <t>1234/XXX-XXX/X1/2025</t>
-  </si>
-  <si>
-    <t>NARATIVE HERE</t>
-  </si>
-  <si>
-    <t>U001</t>
-  </si>
-  <si>
-    <t>1.1.1.1</t>
-  </si>
-  <si>
-    <t>PIC NAME HERE</t>
-  </si>
-  <si>
-    <t>08XXX</t>
-  </si>
-  <si>
-    <t>xxx@bankbjb.co.id</t>
-  </si>
-  <si>
-    <t>D001</t>
-  </si>
-  <si>
-    <t>WORK PROGRAM NAME HERE</t>
-  </si>
-  <si>
-    <t>ACCOUNT NAME HERE</t>
-  </si>
-  <si>
-    <t>01XXXX</t>
+    <t>1255/XXX-XXX/X1/2025</t>
+  </si>
+  <si>
+    <t>IMPLEMENTASI OPLOS ETANOL</t>
+  </si>
+  <si>
+    <t>XXX</t>
+  </si>
+  <si>
+    <t>XX.XX.XXXX</t>
+  </si>
+  <si>
+    <t>XXXXXX</t>
+  </si>
+  <si>
+    <t>089XXX</t>
+  </si>
+  <si>
+    <t>xxxxxxx@bankbjb.co.id</t>
+  </si>
+  <si>
+    <t>XXXX</t>
+  </si>
+  <si>
+    <t>X.X.X.X</t>
+  </si>
+  <si>
+    <t>XXXXXXX</t>
   </si>
   <si>
     <t>XXXXX</t>
   </si>
   <si>
-    <t>WORKPROGRAM NAME HERE</t>
-  </si>
-  <si>
-    <t>02XXX</t>
-  </si>
-  <si>
-    <t>PROJECT CHARACTERISTIC HERE</t>
+    <t>1253/AXA-ERF/X1/2025</t>
   </si>
   <si>
     <t>INTERNAL DEVELOPMENT</t>
   </si>
   <si>
-    <t>INITIATE</t>
-  </si>
-  <si>
-    <t>yyyy/mm/dd</t>
-  </si>
-  <si>
-    <t>U001, U002, ..</t>
-  </si>
-  <si>
-    <t>APPX1</t>
-  </si>
-  <si>
-    <t>APP NAME HERE</t>
-  </si>
-  <si>
-    <t>FITURE1, FITURE2, ...</t>
+    <t>XXXX, XXXX, XXXX</t>
+  </si>
+  <si>
+    <t>XXXXXXXXX</t>
+  </si>
+  <si>
+    <t>LOGIN, DEASHBOARD, AUDIT TRAIL</t>
+  </si>
+  <si>
+    <t>PROCUREMENT</t>
   </si>
 </sst>
 </file>
@@ -251,7 +245,7 @@
     <numFmt numFmtId="176" formatCode="[$Rp-421]#,##0_);[Red]\([$Rp-421]#,##0\)"/>
     <numFmt numFmtId="177" formatCode="[$Rp-421]#,##0;\-[$Rp-421]#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -268,17 +262,41 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFC00000"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="4" tint="-0.5"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -412,7 +430,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="45">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -421,73 +439,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.05"/>
+        <fgColor theme="2" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.25"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor rgb="FF0070C0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -678,12 +636,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -804,137 +777,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -947,65 +920,51 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1540,11 +1499,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AN4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3"/>
+  <dimension ref="A1:AO526"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="22.9140625" customWidth="1"/>
-    <col min="2" max="2" width="18.875" customWidth="1"/>
+    <col min="2" max="2" width="29.625" customWidth="1"/>
     <col min="3" max="3" width="13.1875" customWidth="1"/>
     <col min="4" max="4" width="14.5" customWidth="1"/>
     <col min="5" max="5" width="16.5625" customWidth="1"/>
@@ -1569,387 +1528,368 @@
     <col min="24" max="24" width="37.0625" style="3" customWidth="1"/>
     <col min="25" max="25" width="41.375" style="3" customWidth="1"/>
     <col min="26" max="26" width="25.2578125" customWidth="1"/>
-    <col min="27" max="27" width="27.0625" customWidth="1"/>
-    <col min="28" max="28" width="25.1875" customWidth="1"/>
-    <col min="29" max="29" width="31.6875" customWidth="1"/>
-    <col min="30" max="30" width="22.5234375" customWidth="1"/>
-    <col min="31" max="31" width="28.875" customWidth="1"/>
-    <col min="32" max="32" width="23.1875" customWidth="1"/>
-    <col min="33" max="33" width="31.25" customWidth="1"/>
-    <col min="34" max="34" width="38.9375" customWidth="1"/>
-    <col min="35" max="35" width="25.75" customWidth="1"/>
-    <col min="36" max="36" width="12.1015625" customWidth="1"/>
-    <col min="37" max="37" width="32.625" customWidth="1"/>
-    <col min="38" max="38" width="22.4375" customWidth="1"/>
-    <col min="39" max="39" width="21.375" customWidth="1"/>
-    <col min="40" max="40" width="30.203125" customWidth="1"/>
+    <col min="27" max="27" width="40.5" customWidth="1"/>
+    <col min="28" max="28" width="27.0625" customWidth="1"/>
+    <col min="29" max="29" width="25.1875" customWidth="1"/>
+    <col min="30" max="30" width="54.0625" customWidth="1"/>
+    <col min="31" max="31" width="24.375" customWidth="1"/>
+    <col min="32" max="32" width="28.875" customWidth="1"/>
+    <col min="33" max="33" width="23.1875" customWidth="1"/>
+    <col min="34" max="34" width="31.25" customWidth="1"/>
+    <col min="35" max="35" width="38.9375" customWidth="1"/>
+    <col min="36" max="36" width="25.75" customWidth="1"/>
+    <col min="37" max="37" width="12.1015625" customWidth="1"/>
+    <col min="38" max="38" width="32.625" customWidth="1"/>
+    <col min="39" max="39" width="22.4375" customWidth="1"/>
+    <col min="40" max="40" width="21.375" customWidth="1"/>
+    <col min="41" max="41" width="30.203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:41">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="11" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="14" t="s">
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="14"/>
-      <c r="X1" s="16"/>
-      <c r="Y1" s="16"/>
-      <c r="Z1" s="18" t="s">
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="11"/>
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="18"/>
-      <c r="AB1" s="18"/>
-      <c r="AC1" s="18"/>
-      <c r="AD1" s="18"/>
-      <c r="AE1" s="18"/>
-      <c r="AF1" s="18"/>
-      <c r="AG1" s="18"/>
-      <c r="AH1" s="18"/>
-      <c r="AI1" s="18"/>
-      <c r="AJ1" s="18"/>
-      <c r="AK1" s="18"/>
-      <c r="AL1" s="21" t="s">
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="4"/>
+      <c r="AC1" s="4"/>
+      <c r="AD1" s="4"/>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="4"/>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="4"/>
+      <c r="AI1" s="4"/>
+      <c r="AJ1" s="4"/>
+      <c r="AK1" s="4"/>
+      <c r="AL1" s="4"/>
+      <c r="AM1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="AM1" s="22"/>
-      <c r="AN1" s="22"/>
-    </row>
-    <row r="2" customFormat="1" spans="1:40">
-      <c r="A2" s="6" t="s">
+      <c r="AN1" s="4"/>
+      <c r="AO1" s="4"/>
+    </row>
+    <row r="2" customFormat="1" ht="51" spans="1:41">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="Q2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="R2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="S2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="T2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="U2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="V2" s="6" t="s">
+      <c r="V2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="W2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="X2" s="6" t="s">
+      <c r="X2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="Y2" s="6" t="s">
+      <c r="Y2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="Z2" s="7" t="s">
+      <c r="Z2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AA2" s="7" t="s">
+      <c r="AA2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AB2" s="7" t="s">
+      <c r="AB2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AC2" s="7" t="s">
+      <c r="AC2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AD2" s="7" t="s">
+      <c r="AD2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AE2" s="7" t="s">
+      <c r="AE2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AF2" s="7" t="s">
+      <c r="AF2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AG2" s="7" t="s">
+      <c r="AG2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AH2" s="7" t="s">
+      <c r="AH2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AI2" s="7" t="s">
+      <c r="AI2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AJ2" s="6" t="s">
+      <c r="AJ2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AK2" s="7" t="s">
+      <c r="AK2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="AL2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="AM2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="AN2" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:40">
-      <c r="A3" s="8" t="s">
+      <c r="AM2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="AN2" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="9" t="s">
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:41">
+      <c r="A3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="C3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="D3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="E3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="F3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="G3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="H3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="I3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="J3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="K3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="12" t="s">
+      <c r="L3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="M3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P3" s="13" t="s">
+      <c r="N3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="O3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="R3" s="12" t="s">
+      <c r="P3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="S3" s="15" t="s">
+      <c r="Q3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="T3" s="15" t="s">
+      <c r="R3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="U3" s="15" t="s">
+      <c r="S3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="V3" s="15" t="s">
+      <c r="T3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="W3" s="15" t="s">
+      <c r="U3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="X3" s="17" t="s">
+      <c r="V3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="Y3" s="17" t="s">
+      <c r="W3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="Z3" s="19" t="s">
+      <c r="X3" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="AA3" s="19" t="s">
+      <c r="Y3" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="AB3" s="19" t="s">
+      <c r="Z3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="AC3" s="20" t="s">
+      <c r="AA3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AD3" s="20" t="s">
+      <c r="AB3" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="AE3" s="20" t="s">
+      <c r="AC3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="AF3" s="20" t="s">
+      <c r="AD3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="AG3" s="20" t="s">
+      <c r="AE3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="AH3" s="20" t="s">
+      <c r="AF3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="AI3" s="20" t="s">
+      <c r="AG3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AJ3" s="20" t="s">
+      <c r="AH3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AK3" s="20" t="s">
+      <c r="AI3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="AL3" s="23" t="s">
+      <c r="AJ3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="AM3" s="23" t="s">
+      <c r="AK3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="AN3" s="23" t="s">
+      <c r="AL3" s="6" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="4" spans="1:40">
+      <c r="AM3" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AN3" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO3" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="H4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I4" t="s">
-        <v>55</v>
-      </c>
-      <c r="J4" t="s">
-        <v>51</v>
-      </c>
-      <c r="K4" t="s">
-        <v>56</v>
-      </c>
-      <c r="L4" t="s">
-        <v>57</v>
-      </c>
-      <c r="M4" t="s">
         <v>58</v>
       </c>
-      <c r="N4" t="s">
+      <c r="S4" t="s">
         <v>59</v>
       </c>
-      <c r="O4" s="2">
-        <v>0</v>
-      </c>
-      <c r="P4" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>55</v>
-      </c>
-      <c r="R4" t="s">
-        <v>55</v>
-      </c>
-      <c r="S4" t="s">
-        <v>51</v>
-      </c>
       <c r="T4" t="s">
+        <v>58</v>
+      </c>
+      <c r="U4" t="s">
+        <v>58</v>
+      </c>
+      <c r="V4" t="s">
         <v>60</v>
       </c>
-      <c r="U4" t="s">
-        <v>57</v>
-      </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>61</v>
-      </c>
-      <c r="W4" t="s">
-        <v>59</v>
       </c>
       <c r="X4" s="3">
         <v>0</v>
@@ -1958,58 +1898,1643 @@
         <v>0</v>
       </c>
       <c r="Z4" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="AA4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="AC4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="AD4" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE4" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG4" s="16">
+        <v>45940</v>
+      </c>
+      <c r="AH4" s="16">
+        <v>46305</v>
+      </c>
+      <c r="AI4" s="16">
+        <v>46366</v>
+      </c>
+      <c r="AL4" t="s">
         <v>64</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AM4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN4" t="s">
         <v>65</v>
       </c>
-      <c r="AG4" t="s">
-        <v>65</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>65</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK4" t="s">
+      <c r="AO4" t="s">
         <v>66</v>
       </c>
-      <c r="AL4" t="s">
+    </row>
+    <row r="5" customFormat="1" spans="7:41">
+      <c r="G5" s="7"/>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
+      <c r="Z5"/>
+      <c r="AA5"/>
+      <c r="AB5"/>
+      <c r="AC5"/>
+      <c r="AD5"/>
+      <c r="AE5" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="AM4" t="s">
-        <v>68</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>69</v>
-      </c>
+      <c r="AF5"/>
+      <c r="AG5" s="16"/>
+      <c r="AH5" s="16"/>
+      <c r="AI5" s="16"/>
+      <c r="AO5" s="18"/>
+    </row>
+    <row r="6" spans="31:31">
+      <c r="AE6" s="15"/>
+    </row>
+    <row r="7" spans="31:31">
+      <c r="AE7" s="15"/>
+    </row>
+    <row r="8" spans="31:31">
+      <c r="AE8" s="15"/>
+    </row>
+    <row r="9" spans="31:31">
+      <c r="AE9" s="15"/>
+    </row>
+    <row r="10" spans="31:31">
+      <c r="AE10" s="15"/>
+    </row>
+    <row r="11" spans="31:31">
+      <c r="AE11" s="15"/>
+    </row>
+    <row r="12" spans="31:31">
+      <c r="AE12" s="15"/>
+    </row>
+    <row r="13" spans="31:31">
+      <c r="AE13" s="15"/>
+    </row>
+    <row r="14" spans="31:31">
+      <c r="AE14" s="15"/>
+    </row>
+    <row r="15" spans="31:31">
+      <c r="AE15" s="15"/>
+    </row>
+    <row r="16" spans="31:31">
+      <c r="AE16" s="15"/>
+    </row>
+    <row r="17" spans="31:31">
+      <c r="AE17" s="15"/>
+    </row>
+    <row r="18" spans="31:31">
+      <c r="AE18" s="15"/>
+    </row>
+    <row r="19" spans="31:31">
+      <c r="AE19" s="15"/>
+    </row>
+    <row r="20" spans="31:31">
+      <c r="AE20" s="15"/>
+    </row>
+    <row r="21" spans="31:31">
+      <c r="AE21" s="15"/>
+    </row>
+    <row r="22" spans="31:31">
+      <c r="AE22" s="15"/>
+    </row>
+    <row r="23" spans="31:31">
+      <c r="AE23" s="15"/>
+    </row>
+    <row r="24" spans="31:31">
+      <c r="AE24" s="15"/>
+    </row>
+    <row r="25" spans="31:31">
+      <c r="AE25" s="15"/>
+    </row>
+    <row r="26" spans="31:31">
+      <c r="AE26" s="15"/>
+    </row>
+    <row r="27" spans="31:31">
+      <c r="AE27" s="15"/>
+    </row>
+    <row r="28" spans="31:31">
+      <c r="AE28" s="15"/>
+    </row>
+    <row r="29" spans="31:31">
+      <c r="AE29" s="15"/>
+    </row>
+    <row r="30" spans="31:31">
+      <c r="AE30" s="15"/>
+    </row>
+    <row r="31" spans="31:31">
+      <c r="AE31" s="15"/>
+    </row>
+    <row r="32" spans="31:31">
+      <c r="AE32" s="15"/>
+    </row>
+    <row r="33" spans="31:31">
+      <c r="AE33" s="15"/>
+    </row>
+    <row r="34" spans="31:31">
+      <c r="AE34" s="15"/>
+    </row>
+    <row r="35" spans="31:31">
+      <c r="AE35" s="15"/>
+    </row>
+    <row r="36" spans="31:31">
+      <c r="AE36" s="15"/>
+    </row>
+    <row r="37" spans="31:31">
+      <c r="AE37" s="15"/>
+    </row>
+    <row r="38" spans="31:31">
+      <c r="AE38" s="15"/>
+    </row>
+    <row r="39" spans="31:31">
+      <c r="AE39" s="15"/>
+    </row>
+    <row r="40" spans="31:31">
+      <c r="AE40" s="15"/>
+    </row>
+    <row r="41" spans="31:31">
+      <c r="AE41" s="15"/>
+    </row>
+    <row r="42" spans="31:31">
+      <c r="AE42" s="15"/>
+    </row>
+    <row r="43" spans="31:31">
+      <c r="AE43" s="15"/>
+    </row>
+    <row r="44" spans="31:31">
+      <c r="AE44" s="15"/>
+    </row>
+    <row r="45" spans="31:31">
+      <c r="AE45" s="15"/>
+    </row>
+    <row r="46" spans="31:31">
+      <c r="AE46" s="15"/>
+    </row>
+    <row r="47" spans="31:31">
+      <c r="AE47" s="15"/>
+    </row>
+    <row r="48" spans="31:31">
+      <c r="AE48" s="15"/>
+    </row>
+    <row r="49" spans="31:31">
+      <c r="AE49" s="15"/>
+    </row>
+    <row r="50" spans="31:31">
+      <c r="AE50" s="15"/>
+    </row>
+    <row r="51" spans="31:31">
+      <c r="AE51" s="15"/>
+    </row>
+    <row r="52" spans="31:31">
+      <c r="AE52" s="15"/>
+    </row>
+    <row r="53" spans="31:31">
+      <c r="AE53" s="15"/>
+    </row>
+    <row r="54" spans="31:31">
+      <c r="AE54" s="15"/>
+    </row>
+    <row r="55" spans="31:31">
+      <c r="AE55" s="15"/>
+    </row>
+    <row r="56" spans="31:31">
+      <c r="AE56" s="15"/>
+    </row>
+    <row r="57" spans="31:31">
+      <c r="AE57" s="15"/>
+    </row>
+    <row r="58" spans="31:31">
+      <c r="AE58" s="15"/>
+    </row>
+    <row r="59" spans="31:31">
+      <c r="AE59" s="15"/>
+    </row>
+    <row r="60" spans="31:31">
+      <c r="AE60" s="15"/>
+    </row>
+    <row r="61" spans="31:31">
+      <c r="AE61" s="15"/>
+    </row>
+    <row r="62" spans="31:31">
+      <c r="AE62" s="15"/>
+    </row>
+    <row r="63" spans="31:31">
+      <c r="AE63" s="15"/>
+    </row>
+    <row r="64" spans="31:31">
+      <c r="AE64" s="15"/>
+    </row>
+    <row r="65" spans="31:31">
+      <c r="AE65" s="15"/>
+    </row>
+    <row r="66" spans="31:31">
+      <c r="AE66" s="15"/>
+    </row>
+    <row r="67" spans="31:31">
+      <c r="AE67" s="15"/>
+    </row>
+    <row r="68" spans="31:31">
+      <c r="AE68" s="15"/>
+    </row>
+    <row r="69" spans="31:31">
+      <c r="AE69" s="15"/>
+    </row>
+    <row r="70" spans="31:31">
+      <c r="AE70" s="15"/>
+    </row>
+    <row r="71" spans="31:31">
+      <c r="AE71" s="15"/>
+    </row>
+    <row r="72" spans="31:31">
+      <c r="AE72" s="15"/>
+    </row>
+    <row r="73" spans="31:31">
+      <c r="AE73" s="15"/>
+    </row>
+    <row r="74" spans="31:31">
+      <c r="AE74" s="15"/>
+    </row>
+    <row r="75" spans="31:31">
+      <c r="AE75" s="15"/>
+    </row>
+    <row r="76" spans="31:31">
+      <c r="AE76" s="15"/>
+    </row>
+    <row r="77" spans="31:31">
+      <c r="AE77" s="15"/>
+    </row>
+    <row r="78" spans="31:31">
+      <c r="AE78" s="15"/>
+    </row>
+    <row r="79" spans="31:31">
+      <c r="AE79" s="15"/>
+    </row>
+    <row r="80" spans="31:31">
+      <c r="AE80" s="15"/>
+    </row>
+    <row r="81" spans="31:31">
+      <c r="AE81" s="15"/>
+    </row>
+    <row r="82" spans="31:31">
+      <c r="AE82" s="15"/>
+    </row>
+    <row r="83" spans="31:31">
+      <c r="AE83" s="15"/>
+    </row>
+    <row r="84" spans="31:31">
+      <c r="AE84" s="15"/>
+    </row>
+    <row r="85" spans="31:31">
+      <c r="AE85" s="15"/>
+    </row>
+    <row r="86" spans="31:31">
+      <c r="AE86" s="15"/>
+    </row>
+    <row r="87" spans="31:31">
+      <c r="AE87" s="15"/>
+    </row>
+    <row r="88" spans="31:31">
+      <c r="AE88" s="15"/>
+    </row>
+    <row r="89" spans="31:31">
+      <c r="AE89" s="15"/>
+    </row>
+    <row r="90" spans="31:31">
+      <c r="AE90" s="15"/>
+    </row>
+    <row r="91" spans="31:31">
+      <c r="AE91" s="15"/>
+    </row>
+    <row r="92" spans="31:31">
+      <c r="AE92" s="15"/>
+    </row>
+    <row r="93" spans="31:31">
+      <c r="AE93" s="15"/>
+    </row>
+    <row r="94" spans="31:31">
+      <c r="AE94" s="15"/>
+    </row>
+    <row r="95" spans="31:31">
+      <c r="AE95" s="15"/>
+    </row>
+    <row r="96" spans="31:31">
+      <c r="AE96" s="15"/>
+    </row>
+    <row r="97" spans="31:31">
+      <c r="AE97" s="15"/>
+    </row>
+    <row r="98" spans="31:31">
+      <c r="AE98" s="15"/>
+    </row>
+    <row r="99" spans="31:31">
+      <c r="AE99" s="15"/>
+    </row>
+    <row r="100" spans="31:31">
+      <c r="AE100" s="15"/>
+    </row>
+    <row r="101" spans="31:31">
+      <c r="AE101" s="15"/>
+    </row>
+    <row r="102" spans="31:31">
+      <c r="AE102" s="15"/>
+    </row>
+    <row r="103" spans="31:31">
+      <c r="AE103" s="15"/>
+    </row>
+    <row r="104" spans="31:31">
+      <c r="AE104" s="15"/>
+    </row>
+    <row r="105" spans="31:31">
+      <c r="AE105" s="15"/>
+    </row>
+    <row r="106" spans="31:31">
+      <c r="AE106" s="15"/>
+    </row>
+    <row r="107" spans="31:31">
+      <c r="AE107" s="15"/>
+    </row>
+    <row r="108" spans="31:31">
+      <c r="AE108" s="15"/>
+    </row>
+    <row r="109" spans="31:31">
+      <c r="AE109" s="15"/>
+    </row>
+    <row r="110" spans="31:31">
+      <c r="AE110" s="15"/>
+    </row>
+    <row r="111" spans="31:31">
+      <c r="AE111" s="15"/>
+    </row>
+    <row r="112" spans="31:31">
+      <c r="AE112" s="15"/>
+    </row>
+    <row r="113" spans="31:31">
+      <c r="AE113" s="15"/>
+    </row>
+    <row r="114" spans="31:31">
+      <c r="AE114" s="15"/>
+    </row>
+    <row r="115" spans="31:31">
+      <c r="AE115" s="15"/>
+    </row>
+    <row r="116" spans="31:31">
+      <c r="AE116" s="15"/>
+    </row>
+    <row r="117" spans="31:31">
+      <c r="AE117" s="15"/>
+    </row>
+    <row r="118" spans="31:31">
+      <c r="AE118" s="15"/>
+    </row>
+    <row r="119" spans="31:31">
+      <c r="AE119" s="15"/>
+    </row>
+    <row r="120" spans="31:31">
+      <c r="AE120" s="15"/>
+    </row>
+    <row r="121" spans="31:31">
+      <c r="AE121" s="15"/>
+    </row>
+    <row r="122" spans="31:31">
+      <c r="AE122" s="15"/>
+    </row>
+    <row r="123" spans="31:31">
+      <c r="AE123" s="15"/>
+    </row>
+    <row r="124" spans="31:31">
+      <c r="AE124" s="15"/>
+    </row>
+    <row r="125" spans="31:31">
+      <c r="AE125" s="15"/>
+    </row>
+    <row r="126" spans="31:31">
+      <c r="AE126" s="15"/>
+    </row>
+    <row r="127" spans="31:31">
+      <c r="AE127" s="15"/>
+    </row>
+    <row r="128" spans="31:31">
+      <c r="AE128" s="15"/>
+    </row>
+    <row r="129" spans="31:31">
+      <c r="AE129" s="15"/>
+    </row>
+    <row r="130" spans="31:31">
+      <c r="AE130" s="15"/>
+    </row>
+    <row r="131" spans="31:31">
+      <c r="AE131" s="15"/>
+    </row>
+    <row r="132" spans="31:31">
+      <c r="AE132" s="15"/>
+    </row>
+    <row r="133" spans="31:31">
+      <c r="AE133" s="15"/>
+    </row>
+    <row r="134" spans="31:31">
+      <c r="AE134" s="15"/>
+    </row>
+    <row r="135" spans="31:31">
+      <c r="AE135" s="15"/>
+    </row>
+    <row r="136" spans="31:31">
+      <c r="AE136" s="15"/>
+    </row>
+    <row r="137" spans="31:31">
+      <c r="AE137" s="15"/>
+    </row>
+    <row r="138" spans="31:31">
+      <c r="AE138" s="15"/>
+    </row>
+    <row r="139" spans="31:31">
+      <c r="AE139" s="15"/>
+    </row>
+    <row r="140" spans="31:31">
+      <c r="AE140" s="15"/>
+    </row>
+    <row r="141" spans="31:31">
+      <c r="AE141" s="15"/>
+    </row>
+    <row r="142" spans="31:31">
+      <c r="AE142" s="15"/>
+    </row>
+    <row r="143" spans="31:31">
+      <c r="AE143" s="15"/>
+    </row>
+    <row r="144" spans="31:31">
+      <c r="AE144" s="15"/>
+    </row>
+    <row r="145" spans="31:31">
+      <c r="AE145" s="15"/>
+    </row>
+    <row r="146" spans="31:31">
+      <c r="AE146" s="15"/>
+    </row>
+    <row r="147" spans="31:31">
+      <c r="AE147" s="15"/>
+    </row>
+    <row r="148" spans="31:31">
+      <c r="AE148" s="15"/>
+    </row>
+    <row r="149" spans="31:31">
+      <c r="AE149" s="15"/>
+    </row>
+    <row r="150" spans="31:31">
+      <c r="AE150" s="15"/>
+    </row>
+    <row r="151" spans="31:31">
+      <c r="AE151" s="15"/>
+    </row>
+    <row r="152" spans="31:31">
+      <c r="AE152" s="15"/>
+    </row>
+    <row r="153" spans="31:31">
+      <c r="AE153" s="15"/>
+    </row>
+    <row r="154" spans="31:31">
+      <c r="AE154" s="15"/>
+    </row>
+    <row r="155" spans="31:31">
+      <c r="AE155" s="15"/>
+    </row>
+    <row r="156" spans="31:31">
+      <c r="AE156" s="15"/>
+    </row>
+    <row r="157" spans="31:31">
+      <c r="AE157" s="15"/>
+    </row>
+    <row r="158" spans="31:31">
+      <c r="AE158" s="15"/>
+    </row>
+    <row r="159" spans="31:31">
+      <c r="AE159" s="15"/>
+    </row>
+    <row r="160" spans="31:31">
+      <c r="AE160" s="15"/>
+    </row>
+    <row r="161" spans="31:31">
+      <c r="AE161" s="15"/>
+    </row>
+    <row r="162" spans="31:31">
+      <c r="AE162" s="15"/>
+    </row>
+    <row r="163" spans="31:31">
+      <c r="AE163" s="15"/>
+    </row>
+    <row r="164" spans="31:31">
+      <c r="AE164" s="15"/>
+    </row>
+    <row r="165" spans="31:31">
+      <c r="AE165" s="15"/>
+    </row>
+    <row r="166" spans="31:31">
+      <c r="AE166" s="15"/>
+    </row>
+    <row r="167" spans="31:31">
+      <c r="AE167" s="15"/>
+    </row>
+    <row r="168" spans="31:31">
+      <c r="AE168" s="15"/>
+    </row>
+    <row r="169" spans="31:31">
+      <c r="AE169" s="15"/>
+    </row>
+    <row r="170" spans="31:31">
+      <c r="AE170" s="15"/>
+    </row>
+    <row r="171" spans="31:31">
+      <c r="AE171" s="15"/>
+    </row>
+    <row r="172" spans="31:31">
+      <c r="AE172" s="15"/>
+    </row>
+    <row r="173" spans="31:31">
+      <c r="AE173" s="15"/>
+    </row>
+    <row r="174" spans="31:31">
+      <c r="AE174" s="15"/>
+    </row>
+    <row r="175" spans="31:31">
+      <c r="AE175" s="15"/>
+    </row>
+    <row r="176" spans="31:31">
+      <c r="AE176" s="15"/>
+    </row>
+    <row r="177" spans="31:31">
+      <c r="AE177" s="15"/>
+    </row>
+    <row r="178" spans="31:31">
+      <c r="AE178" s="15"/>
+    </row>
+    <row r="179" spans="31:31">
+      <c r="AE179" s="15"/>
+    </row>
+    <row r="180" spans="31:31">
+      <c r="AE180" s="15"/>
+    </row>
+    <row r="181" spans="31:31">
+      <c r="AE181" s="15"/>
+    </row>
+    <row r="182" spans="31:31">
+      <c r="AE182" s="15"/>
+    </row>
+    <row r="183" spans="31:31">
+      <c r="AE183" s="15"/>
+    </row>
+    <row r="184" spans="31:31">
+      <c r="AE184" s="15"/>
+    </row>
+    <row r="185" spans="31:31">
+      <c r="AE185" s="15"/>
+    </row>
+    <row r="186" spans="31:31">
+      <c r="AE186" s="15"/>
+    </row>
+    <row r="187" spans="31:31">
+      <c r="AE187" s="15"/>
+    </row>
+    <row r="188" spans="31:31">
+      <c r="AE188" s="15"/>
+    </row>
+    <row r="189" spans="31:31">
+      <c r="AE189" s="15"/>
+    </row>
+    <row r="190" spans="31:31">
+      <c r="AE190" s="15"/>
+    </row>
+    <row r="191" spans="31:31">
+      <c r="AE191" s="15"/>
+    </row>
+    <row r="192" spans="31:31">
+      <c r="AE192" s="15"/>
+    </row>
+    <row r="193" spans="31:31">
+      <c r="AE193" s="15"/>
+    </row>
+    <row r="194" spans="31:31">
+      <c r="AE194" s="15"/>
+    </row>
+    <row r="195" spans="31:31">
+      <c r="AE195" s="15"/>
+    </row>
+    <row r="196" spans="31:31">
+      <c r="AE196" s="15"/>
+    </row>
+    <row r="197" spans="31:31">
+      <c r="AE197" s="15"/>
+    </row>
+    <row r="198" spans="31:31">
+      <c r="AE198" s="15"/>
+    </row>
+    <row r="199" spans="31:31">
+      <c r="AE199" s="15"/>
+    </row>
+    <row r="200" spans="31:31">
+      <c r="AE200" s="15"/>
+    </row>
+    <row r="201" spans="31:31">
+      <c r="AE201" s="15"/>
+    </row>
+    <row r="202" spans="31:31">
+      <c r="AE202" s="15"/>
+    </row>
+    <row r="203" spans="31:31">
+      <c r="AE203" s="15"/>
+    </row>
+    <row r="204" spans="31:31">
+      <c r="AE204" s="15"/>
+    </row>
+    <row r="205" spans="31:31">
+      <c r="AE205" s="15"/>
+    </row>
+    <row r="206" spans="31:31">
+      <c r="AE206" s="15"/>
+    </row>
+    <row r="207" spans="31:31">
+      <c r="AE207" s="15"/>
+    </row>
+    <row r="208" spans="31:31">
+      <c r="AE208" s="15"/>
+    </row>
+    <row r="209" spans="31:31">
+      <c r="AE209" s="15"/>
+    </row>
+    <row r="210" spans="31:31">
+      <c r="AE210" s="15"/>
+    </row>
+    <row r="211" spans="31:31">
+      <c r="AE211" s="15"/>
+    </row>
+    <row r="212" spans="31:31">
+      <c r="AE212" s="15"/>
+    </row>
+    <row r="213" spans="31:31">
+      <c r="AE213" s="15"/>
+    </row>
+    <row r="214" spans="31:31">
+      <c r="AE214" s="15"/>
+    </row>
+    <row r="215" spans="31:31">
+      <c r="AE215" s="15"/>
+    </row>
+    <row r="216" spans="31:31">
+      <c r="AE216" s="15"/>
+    </row>
+    <row r="217" spans="31:31">
+      <c r="AE217" s="15"/>
+    </row>
+    <row r="218" spans="31:31">
+      <c r="AE218" s="15"/>
+    </row>
+    <row r="219" spans="31:31">
+      <c r="AE219" s="15"/>
+    </row>
+    <row r="220" spans="31:31">
+      <c r="AE220" s="15"/>
+    </row>
+    <row r="221" spans="31:31">
+      <c r="AE221" s="15"/>
+    </row>
+    <row r="222" spans="31:31">
+      <c r="AE222" s="15"/>
+    </row>
+    <row r="223" spans="31:31">
+      <c r="AE223" s="15"/>
+    </row>
+    <row r="224" spans="31:31">
+      <c r="AE224" s="15"/>
+    </row>
+    <row r="225" spans="31:31">
+      <c r="AE225" s="15"/>
+    </row>
+    <row r="226" spans="31:31">
+      <c r="AE226" s="15"/>
+    </row>
+    <row r="227" spans="31:31">
+      <c r="AE227" s="15"/>
+    </row>
+    <row r="228" spans="31:31">
+      <c r="AE228" s="15"/>
+    </row>
+    <row r="229" spans="31:31">
+      <c r="AE229" s="15"/>
+    </row>
+    <row r="230" spans="31:31">
+      <c r="AE230" s="15"/>
+    </row>
+    <row r="231" spans="31:31">
+      <c r="AE231" s="15"/>
+    </row>
+    <row r="232" spans="31:31">
+      <c r="AE232" s="15"/>
+    </row>
+    <row r="233" spans="31:31">
+      <c r="AE233" s="15"/>
+    </row>
+    <row r="234" spans="31:31">
+      <c r="AE234" s="15"/>
+    </row>
+    <row r="235" spans="31:31">
+      <c r="AE235" s="15"/>
+    </row>
+    <row r="236" spans="31:31">
+      <c r="AE236" s="15"/>
+    </row>
+    <row r="237" spans="31:31">
+      <c r="AE237" s="15"/>
+    </row>
+    <row r="238" spans="31:31">
+      <c r="AE238" s="15"/>
+    </row>
+    <row r="239" spans="31:31">
+      <c r="AE239" s="15"/>
+    </row>
+    <row r="240" spans="31:31">
+      <c r="AE240" s="15"/>
+    </row>
+    <row r="241" spans="31:31">
+      <c r="AE241" s="15"/>
+    </row>
+    <row r="242" spans="31:31">
+      <c r="AE242" s="15"/>
+    </row>
+    <row r="243" spans="31:31">
+      <c r="AE243" s="15"/>
+    </row>
+    <row r="244" spans="31:31">
+      <c r="AE244" s="15"/>
+    </row>
+    <row r="245" spans="31:31">
+      <c r="AE245" s="15"/>
+    </row>
+    <row r="246" spans="31:31">
+      <c r="AE246" s="15"/>
+    </row>
+    <row r="247" spans="31:31">
+      <c r="AE247" s="15"/>
+    </row>
+    <row r="248" spans="31:31">
+      <c r="AE248" s="15"/>
+    </row>
+    <row r="249" spans="31:31">
+      <c r="AE249" s="15"/>
+    </row>
+    <row r="250" spans="31:31">
+      <c r="AE250" s="15"/>
+    </row>
+    <row r="251" spans="31:31">
+      <c r="AE251" s="15"/>
+    </row>
+    <row r="252" spans="31:31">
+      <c r="AE252" s="15"/>
+    </row>
+    <row r="253" spans="31:31">
+      <c r="AE253" s="15"/>
+    </row>
+    <row r="254" spans="31:31">
+      <c r="AE254" s="15"/>
+    </row>
+    <row r="255" spans="31:31">
+      <c r="AE255" s="15"/>
+    </row>
+    <row r="256" spans="31:31">
+      <c r="AE256" s="15"/>
+    </row>
+    <row r="257" spans="31:31">
+      <c r="AE257" s="15"/>
+    </row>
+    <row r="258" spans="31:31">
+      <c r="AE258" s="15"/>
+    </row>
+    <row r="259" spans="31:31">
+      <c r="AE259" s="15"/>
+    </row>
+    <row r="260" spans="31:31">
+      <c r="AE260" s="15"/>
+    </row>
+    <row r="261" spans="31:31">
+      <c r="AE261" s="15"/>
+    </row>
+    <row r="262" spans="31:31">
+      <c r="AE262" s="15"/>
+    </row>
+    <row r="263" spans="31:31">
+      <c r="AE263" s="15"/>
+    </row>
+    <row r="264" spans="31:31">
+      <c r="AE264" s="15"/>
+    </row>
+    <row r="265" spans="31:31">
+      <c r="AE265" s="15"/>
+    </row>
+    <row r="266" spans="31:31">
+      <c r="AE266" s="15"/>
+    </row>
+    <row r="267" spans="31:31">
+      <c r="AE267" s="15"/>
+    </row>
+    <row r="268" spans="31:31">
+      <c r="AE268" s="15"/>
+    </row>
+    <row r="269" spans="31:31">
+      <c r="AE269" s="15"/>
+    </row>
+    <row r="270" spans="31:31">
+      <c r="AE270" s="15"/>
+    </row>
+    <row r="271" spans="31:31">
+      <c r="AE271" s="15"/>
+    </row>
+    <row r="272" spans="31:31">
+      <c r="AE272" s="15"/>
+    </row>
+    <row r="273" spans="31:31">
+      <c r="AE273" s="15"/>
+    </row>
+    <row r="274" spans="31:31">
+      <c r="AE274" s="15"/>
+    </row>
+    <row r="275" spans="31:31">
+      <c r="AE275" s="15"/>
+    </row>
+    <row r="276" spans="31:31">
+      <c r="AE276" s="15"/>
+    </row>
+    <row r="277" spans="31:31">
+      <c r="AE277" s="15"/>
+    </row>
+    <row r="278" spans="31:31">
+      <c r="AE278" s="15"/>
+    </row>
+    <row r="279" spans="31:31">
+      <c r="AE279" s="15"/>
+    </row>
+    <row r="280" spans="31:31">
+      <c r="AE280" s="15"/>
+    </row>
+    <row r="281" spans="31:31">
+      <c r="AE281" s="15"/>
+    </row>
+    <row r="282" spans="31:31">
+      <c r="AE282" s="15"/>
+    </row>
+    <row r="283" spans="31:31">
+      <c r="AE283" s="15"/>
+    </row>
+    <row r="284" spans="31:31">
+      <c r="AE284" s="15"/>
+    </row>
+    <row r="285" spans="31:31">
+      <c r="AE285" s="15"/>
+    </row>
+    <row r="286" spans="31:31">
+      <c r="AE286" s="15"/>
+    </row>
+    <row r="287" spans="31:31">
+      <c r="AE287" s="15"/>
+    </row>
+    <row r="288" spans="31:31">
+      <c r="AE288" s="15"/>
+    </row>
+    <row r="289" spans="31:31">
+      <c r="AE289" s="15"/>
+    </row>
+    <row r="290" spans="31:31">
+      <c r="AE290" s="15"/>
+    </row>
+    <row r="291" spans="31:31">
+      <c r="AE291" s="15"/>
+    </row>
+    <row r="292" spans="31:31">
+      <c r="AE292" s="15"/>
+    </row>
+    <row r="293" spans="31:31">
+      <c r="AE293" s="15"/>
+    </row>
+    <row r="294" spans="31:31">
+      <c r="AE294" s="15"/>
+    </row>
+    <row r="295" spans="31:31">
+      <c r="AE295" s="15"/>
+    </row>
+    <row r="296" spans="31:31">
+      <c r="AE296" s="15"/>
+    </row>
+    <row r="297" spans="31:31">
+      <c r="AE297" s="15"/>
+    </row>
+    <row r="298" spans="31:31">
+      <c r="AE298" s="15"/>
+    </row>
+    <row r="299" spans="31:31">
+      <c r="AE299" s="15"/>
+    </row>
+    <row r="300" spans="31:31">
+      <c r="AE300" s="15"/>
+    </row>
+    <row r="301" spans="31:31">
+      <c r="AE301" s="15"/>
+    </row>
+    <row r="302" spans="31:31">
+      <c r="AE302" s="15"/>
+    </row>
+    <row r="303" spans="31:31">
+      <c r="AE303" s="15"/>
+    </row>
+    <row r="304" spans="31:31">
+      <c r="AE304" s="15"/>
+    </row>
+    <row r="305" spans="31:31">
+      <c r="AE305" s="15"/>
+    </row>
+    <row r="306" spans="31:31">
+      <c r="AE306" s="15"/>
+    </row>
+    <row r="307" spans="31:31">
+      <c r="AE307" s="15"/>
+    </row>
+    <row r="308" spans="31:31">
+      <c r="AE308" s="15"/>
+    </row>
+    <row r="309" spans="31:31">
+      <c r="AE309" s="15"/>
+    </row>
+    <row r="310" spans="31:31">
+      <c r="AE310" s="15"/>
+    </row>
+    <row r="311" spans="31:31">
+      <c r="AE311" s="15"/>
+    </row>
+    <row r="312" spans="31:31">
+      <c r="AE312" s="15"/>
+    </row>
+    <row r="313" spans="31:31">
+      <c r="AE313" s="15"/>
+    </row>
+    <row r="314" spans="31:31">
+      <c r="AE314" s="15"/>
+    </row>
+    <row r="315" spans="31:31">
+      <c r="AE315" s="15"/>
+    </row>
+    <row r="316" spans="31:31">
+      <c r="AE316" s="15"/>
+    </row>
+    <row r="317" spans="31:31">
+      <c r="AE317" s="15"/>
+    </row>
+    <row r="318" spans="31:31">
+      <c r="AE318" s="15"/>
+    </row>
+    <row r="319" spans="31:31">
+      <c r="AE319" s="15"/>
+    </row>
+    <row r="320" spans="31:31">
+      <c r="AE320" s="15"/>
+    </row>
+    <row r="321" spans="31:31">
+      <c r="AE321" s="15"/>
+    </row>
+    <row r="322" spans="31:31">
+      <c r="AE322" s="15"/>
+    </row>
+    <row r="323" spans="31:31">
+      <c r="AE323" s="15"/>
+    </row>
+    <row r="324" spans="31:31">
+      <c r="AE324" s="15"/>
+    </row>
+    <row r="325" spans="31:31">
+      <c r="AE325" s="15"/>
+    </row>
+    <row r="326" spans="31:31">
+      <c r="AE326" s="15"/>
+    </row>
+    <row r="327" spans="31:31">
+      <c r="AE327" s="15"/>
+    </row>
+    <row r="328" spans="31:31">
+      <c r="AE328" s="15"/>
+    </row>
+    <row r="329" spans="31:31">
+      <c r="AE329" s="15"/>
+    </row>
+    <row r="330" spans="31:31">
+      <c r="AE330" s="15"/>
+    </row>
+    <row r="331" spans="31:31">
+      <c r="AE331" s="15"/>
+    </row>
+    <row r="332" spans="31:31">
+      <c r="AE332" s="15"/>
+    </row>
+    <row r="333" spans="31:31">
+      <c r="AE333" s="15"/>
+    </row>
+    <row r="334" spans="31:31">
+      <c r="AE334" s="15"/>
+    </row>
+    <row r="335" spans="31:31">
+      <c r="AE335" s="15"/>
+    </row>
+    <row r="336" spans="31:31">
+      <c r="AE336" s="15"/>
+    </row>
+    <row r="337" spans="31:31">
+      <c r="AE337" s="15"/>
+    </row>
+    <row r="338" spans="31:31">
+      <c r="AE338" s="15"/>
+    </row>
+    <row r="339" spans="31:31">
+      <c r="AE339" s="15"/>
+    </row>
+    <row r="340" spans="31:31">
+      <c r="AE340" s="15"/>
+    </row>
+    <row r="341" spans="31:31">
+      <c r="AE341" s="15"/>
+    </row>
+    <row r="342" spans="31:31">
+      <c r="AE342" s="15"/>
+    </row>
+    <row r="343" spans="31:31">
+      <c r="AE343" s="15"/>
+    </row>
+    <row r="344" spans="31:31">
+      <c r="AE344" s="15"/>
+    </row>
+    <row r="345" spans="31:31">
+      <c r="AE345" s="15"/>
+    </row>
+    <row r="346" spans="31:31">
+      <c r="AE346" s="15"/>
+    </row>
+    <row r="347" spans="31:31">
+      <c r="AE347" s="15"/>
+    </row>
+    <row r="348" spans="31:31">
+      <c r="AE348" s="15"/>
+    </row>
+    <row r="349" spans="31:31">
+      <c r="AE349" s="15"/>
+    </row>
+    <row r="350" spans="31:31">
+      <c r="AE350" s="15"/>
+    </row>
+    <row r="351" spans="31:31">
+      <c r="AE351" s="15"/>
+    </row>
+    <row r="352" spans="31:31">
+      <c r="AE352" s="15"/>
+    </row>
+    <row r="353" spans="31:31">
+      <c r="AE353" s="15"/>
+    </row>
+    <row r="354" spans="31:31">
+      <c r="AE354" s="15"/>
+    </row>
+    <row r="355" spans="31:31">
+      <c r="AE355" s="15"/>
+    </row>
+    <row r="356" spans="31:31">
+      <c r="AE356" s="15"/>
+    </row>
+    <row r="357" spans="31:31">
+      <c r="AE357" s="15"/>
+    </row>
+    <row r="358" spans="31:31">
+      <c r="AE358" s="15"/>
+    </row>
+    <row r="359" spans="31:31">
+      <c r="AE359" s="15"/>
+    </row>
+    <row r="360" spans="31:31">
+      <c r="AE360" s="15"/>
+    </row>
+    <row r="361" spans="31:31">
+      <c r="AE361" s="15"/>
+    </row>
+    <row r="362" spans="31:31">
+      <c r="AE362" s="15"/>
+    </row>
+    <row r="363" spans="31:31">
+      <c r="AE363" s="15"/>
+    </row>
+    <row r="364" spans="31:31">
+      <c r="AE364" s="15"/>
+    </row>
+    <row r="365" spans="31:31">
+      <c r="AE365" s="15"/>
+    </row>
+    <row r="366" spans="31:31">
+      <c r="AE366" s="15"/>
+    </row>
+    <row r="367" spans="31:31">
+      <c r="AE367" s="15"/>
+    </row>
+    <row r="368" spans="31:31">
+      <c r="AE368" s="15"/>
+    </row>
+    <row r="369" spans="31:31">
+      <c r="AE369" s="15"/>
+    </row>
+    <row r="370" spans="31:31">
+      <c r="AE370" s="15"/>
+    </row>
+    <row r="371" spans="31:31">
+      <c r="AE371" s="15"/>
+    </row>
+    <row r="372" spans="31:31">
+      <c r="AE372" s="15"/>
+    </row>
+    <row r="373" spans="31:31">
+      <c r="AE373" s="15"/>
+    </row>
+    <row r="374" spans="31:31">
+      <c r="AE374" s="15"/>
+    </row>
+    <row r="375" spans="31:31">
+      <c r="AE375" s="15"/>
+    </row>
+    <row r="376" spans="31:31">
+      <c r="AE376" s="15"/>
+    </row>
+    <row r="377" spans="31:31">
+      <c r="AE377" s="15"/>
+    </row>
+    <row r="378" spans="31:31">
+      <c r="AE378" s="15"/>
+    </row>
+    <row r="379" spans="31:31">
+      <c r="AE379" s="15"/>
+    </row>
+    <row r="380" spans="31:31">
+      <c r="AE380" s="15"/>
+    </row>
+    <row r="381" spans="31:31">
+      <c r="AE381" s="15"/>
+    </row>
+    <row r="382" spans="31:31">
+      <c r="AE382" s="15"/>
+    </row>
+    <row r="383" spans="31:31">
+      <c r="AE383" s="15"/>
+    </row>
+    <row r="384" spans="31:31">
+      <c r="AE384" s="15"/>
+    </row>
+    <row r="385" spans="31:31">
+      <c r="AE385" s="15"/>
+    </row>
+    <row r="386" spans="31:31">
+      <c r="AE386" s="15"/>
+    </row>
+    <row r="387" spans="31:31">
+      <c r="AE387" s="15"/>
+    </row>
+    <row r="388" spans="31:31">
+      <c r="AE388" s="15"/>
+    </row>
+    <row r="389" spans="31:31">
+      <c r="AE389" s="15"/>
+    </row>
+    <row r="390" spans="31:31">
+      <c r="AE390" s="15"/>
+    </row>
+    <row r="391" spans="31:31">
+      <c r="AE391" s="15"/>
+    </row>
+    <row r="392" spans="31:31">
+      <c r="AE392" s="15"/>
+    </row>
+    <row r="393" spans="31:31">
+      <c r="AE393" s="15"/>
+    </row>
+    <row r="394" spans="31:31">
+      <c r="AE394" s="15"/>
+    </row>
+    <row r="395" spans="31:31">
+      <c r="AE395" s="15"/>
+    </row>
+    <row r="396" spans="31:31">
+      <c r="AE396" s="15"/>
+    </row>
+    <row r="397" spans="31:31">
+      <c r="AE397" s="15"/>
+    </row>
+    <row r="398" spans="31:31">
+      <c r="AE398" s="15"/>
+    </row>
+    <row r="399" spans="31:31">
+      <c r="AE399" s="15"/>
+    </row>
+    <row r="400" spans="31:31">
+      <c r="AE400" s="15"/>
+    </row>
+    <row r="401" spans="31:31">
+      <c r="AE401" s="15"/>
+    </row>
+    <row r="402" spans="31:31">
+      <c r="AE402" s="15"/>
+    </row>
+    <row r="403" spans="31:31">
+      <c r="AE403" s="15"/>
+    </row>
+    <row r="404" spans="31:31">
+      <c r="AE404" s="15"/>
+    </row>
+    <row r="405" spans="31:31">
+      <c r="AE405" s="15"/>
+    </row>
+    <row r="406" spans="31:31">
+      <c r="AE406" s="15"/>
+    </row>
+    <row r="407" spans="31:31">
+      <c r="AE407" s="15"/>
+    </row>
+    <row r="408" spans="31:31">
+      <c r="AE408" s="15"/>
+    </row>
+    <row r="409" spans="31:31">
+      <c r="AE409" s="15"/>
+    </row>
+    <row r="410" spans="31:31">
+      <c r="AE410" s="15"/>
+    </row>
+    <row r="411" spans="31:31">
+      <c r="AE411" s="15"/>
+    </row>
+    <row r="412" spans="31:31">
+      <c r="AE412" s="15"/>
+    </row>
+    <row r="413" spans="31:31">
+      <c r="AE413" s="15"/>
+    </row>
+    <row r="414" spans="31:31">
+      <c r="AE414" s="15"/>
+    </row>
+    <row r="415" spans="31:31">
+      <c r="AE415" s="15"/>
+    </row>
+    <row r="416" spans="31:31">
+      <c r="AE416" s="15"/>
+    </row>
+    <row r="417" spans="31:31">
+      <c r="AE417" s="15"/>
+    </row>
+    <row r="418" spans="31:31">
+      <c r="AE418" s="15"/>
+    </row>
+    <row r="419" spans="31:31">
+      <c r="AE419" s="15"/>
+    </row>
+    <row r="420" spans="31:31">
+      <c r="AE420" s="15"/>
+    </row>
+    <row r="421" spans="31:31">
+      <c r="AE421" s="15"/>
+    </row>
+    <row r="422" spans="31:31">
+      <c r="AE422" s="15"/>
+    </row>
+    <row r="423" spans="31:31">
+      <c r="AE423" s="15"/>
+    </row>
+    <row r="424" spans="31:31">
+      <c r="AE424" s="15"/>
+    </row>
+    <row r="425" spans="31:31">
+      <c r="AE425" s="15"/>
+    </row>
+    <row r="426" spans="31:31">
+      <c r="AE426" s="15"/>
+    </row>
+    <row r="427" spans="31:31">
+      <c r="AE427" s="15"/>
+    </row>
+    <row r="428" spans="31:31">
+      <c r="AE428" s="15"/>
+    </row>
+    <row r="429" spans="31:31">
+      <c r="AE429" s="15"/>
+    </row>
+    <row r="430" spans="31:31">
+      <c r="AE430" s="15"/>
+    </row>
+    <row r="431" spans="31:31">
+      <c r="AE431" s="15"/>
+    </row>
+    <row r="432" spans="31:31">
+      <c r="AE432" s="15"/>
+    </row>
+    <row r="433" spans="31:31">
+      <c r="AE433" s="15"/>
+    </row>
+    <row r="434" spans="31:31">
+      <c r="AE434" s="15"/>
+    </row>
+    <row r="435" spans="31:31">
+      <c r="AE435" s="15"/>
+    </row>
+    <row r="436" spans="31:31">
+      <c r="AE436" s="15"/>
+    </row>
+    <row r="437" spans="31:31">
+      <c r="AE437" s="15"/>
+    </row>
+    <row r="438" spans="31:31">
+      <c r="AE438" s="15"/>
+    </row>
+    <row r="439" spans="31:31">
+      <c r="AE439" s="15"/>
+    </row>
+    <row r="440" spans="31:31">
+      <c r="AE440" s="15"/>
+    </row>
+    <row r="441" spans="31:31">
+      <c r="AE441" s="15"/>
+    </row>
+    <row r="442" spans="31:31">
+      <c r="AE442" s="15"/>
+    </row>
+    <row r="443" spans="31:31">
+      <c r="AE443" s="15"/>
+    </row>
+    <row r="444" spans="31:31">
+      <c r="AE444" s="15"/>
+    </row>
+    <row r="445" spans="31:31">
+      <c r="AE445" s="15"/>
+    </row>
+    <row r="446" spans="31:31">
+      <c r="AE446" s="15"/>
+    </row>
+    <row r="447" spans="31:31">
+      <c r="AE447" s="15"/>
+    </row>
+    <row r="448" spans="31:31">
+      <c r="AE448" s="15"/>
+    </row>
+    <row r="449" spans="31:31">
+      <c r="AE449" s="15"/>
+    </row>
+    <row r="450" spans="31:31">
+      <c r="AE450" s="15"/>
+    </row>
+    <row r="451" spans="31:31">
+      <c r="AE451" s="15"/>
+    </row>
+    <row r="452" spans="31:31">
+      <c r="AE452" s="15"/>
+    </row>
+    <row r="453" spans="31:31">
+      <c r="AE453" s="15"/>
+    </row>
+    <row r="454" spans="31:31">
+      <c r="AE454" s="15"/>
+    </row>
+    <row r="455" spans="31:31">
+      <c r="AE455" s="15"/>
+    </row>
+    <row r="456" spans="31:31">
+      <c r="AE456" s="15"/>
+    </row>
+    <row r="457" spans="31:31">
+      <c r="AE457" s="15"/>
+    </row>
+    <row r="458" spans="31:31">
+      <c r="AE458" s="15"/>
+    </row>
+    <row r="459" spans="31:31">
+      <c r="AE459" s="15"/>
+    </row>
+    <row r="460" spans="31:31">
+      <c r="AE460" s="15"/>
+    </row>
+    <row r="461" spans="31:31">
+      <c r="AE461" s="15"/>
+    </row>
+    <row r="462" spans="31:31">
+      <c r="AE462" s="15"/>
+    </row>
+    <row r="463" spans="31:31">
+      <c r="AE463" s="15"/>
+    </row>
+    <row r="464" spans="31:31">
+      <c r="AE464" s="15"/>
+    </row>
+    <row r="465" spans="31:31">
+      <c r="AE465" s="15"/>
+    </row>
+    <row r="466" spans="31:31">
+      <c r="AE466" s="15"/>
+    </row>
+    <row r="467" spans="31:31">
+      <c r="AE467" s="15"/>
+    </row>
+    <row r="468" spans="31:31">
+      <c r="AE468" s="15"/>
+    </row>
+    <row r="469" spans="31:31">
+      <c r="AE469" s="15"/>
+    </row>
+    <row r="470" spans="31:31">
+      <c r="AE470" s="15"/>
+    </row>
+    <row r="471" spans="31:31">
+      <c r="AE471" s="15"/>
+    </row>
+    <row r="472" spans="31:31">
+      <c r="AE472" s="15"/>
+    </row>
+    <row r="473" spans="31:31">
+      <c r="AE473" s="15"/>
+    </row>
+    <row r="474" spans="31:31">
+      <c r="AE474" s="15"/>
+    </row>
+    <row r="475" spans="31:31">
+      <c r="AE475" s="15"/>
+    </row>
+    <row r="476" spans="31:31">
+      <c r="AE476" s="15"/>
+    </row>
+    <row r="477" spans="31:31">
+      <c r="AE477" s="15"/>
+    </row>
+    <row r="478" spans="31:31">
+      <c r="AE478" s="15"/>
+    </row>
+    <row r="479" spans="31:31">
+      <c r="AE479" s="15"/>
+    </row>
+    <row r="480" spans="31:31">
+      <c r="AE480" s="15"/>
+    </row>
+    <row r="481" spans="31:31">
+      <c r="AE481" s="15"/>
+    </row>
+    <row r="482" spans="31:31">
+      <c r="AE482" s="15"/>
+    </row>
+    <row r="483" spans="31:31">
+      <c r="AE483" s="15"/>
+    </row>
+    <row r="484" spans="31:31">
+      <c r="AE484" s="15"/>
+    </row>
+    <row r="485" spans="31:31">
+      <c r="AE485" s="15"/>
+    </row>
+    <row r="486" spans="31:31">
+      <c r="AE486" s="15"/>
+    </row>
+    <row r="487" spans="31:31">
+      <c r="AE487" s="15"/>
+    </row>
+    <row r="488" spans="31:31">
+      <c r="AE488" s="15"/>
+    </row>
+    <row r="489" spans="31:31">
+      <c r="AE489" s="15"/>
+    </row>
+    <row r="490" spans="31:31">
+      <c r="AE490" s="15"/>
+    </row>
+    <row r="491" spans="31:31">
+      <c r="AE491" s="15"/>
+    </row>
+    <row r="492" spans="31:31">
+      <c r="AE492" s="15"/>
+    </row>
+    <row r="493" spans="31:31">
+      <c r="AE493" s="15"/>
+    </row>
+    <row r="494" spans="31:31">
+      <c r="AE494" s="15"/>
+    </row>
+    <row r="495" spans="31:31">
+      <c r="AE495" s="15"/>
+    </row>
+    <row r="496" spans="31:31">
+      <c r="AE496" s="15"/>
+    </row>
+    <row r="497" spans="31:31">
+      <c r="AE497" s="15"/>
+    </row>
+    <row r="498" spans="31:31">
+      <c r="AE498" s="15"/>
+    </row>
+    <row r="499" spans="31:31">
+      <c r="AE499" s="15"/>
+    </row>
+    <row r="500" spans="31:31">
+      <c r="AE500" s="15"/>
+    </row>
+    <row r="501" spans="31:31">
+      <c r="AE501" s="15"/>
+    </row>
+    <row r="502" spans="31:31">
+      <c r="AE502" s="15"/>
+    </row>
+    <row r="503" spans="31:31">
+      <c r="AE503" s="15"/>
+    </row>
+    <row r="504" spans="31:31">
+      <c r="AE504" s="15"/>
+    </row>
+    <row r="505" spans="31:31">
+      <c r="AE505" s="15"/>
+    </row>
+    <row r="506" spans="31:31">
+      <c r="AE506" s="15"/>
+    </row>
+    <row r="507" spans="31:31">
+      <c r="AE507" s="15"/>
+    </row>
+    <row r="508" spans="31:31">
+      <c r="AE508" s="15"/>
+    </row>
+    <row r="509" spans="31:31">
+      <c r="AE509" s="15"/>
+    </row>
+    <row r="510" spans="31:31">
+      <c r="AE510" s="15"/>
+    </row>
+    <row r="511" spans="31:31">
+      <c r="AE511" s="15"/>
+    </row>
+    <row r="512" spans="31:31">
+      <c r="AE512" s="15"/>
+    </row>
+    <row r="513" spans="31:31">
+      <c r="AE513" s="15"/>
+    </row>
+    <row r="514" spans="31:31">
+      <c r="AE514" s="15"/>
+    </row>
+    <row r="515" spans="31:31">
+      <c r="AE515" s="15"/>
+    </row>
+    <row r="516" spans="31:31">
+      <c r="AE516" s="15"/>
+    </row>
+    <row r="517" spans="31:31">
+      <c r="AE517" s="15"/>
+    </row>
+    <row r="518" spans="31:31">
+      <c r="AE518" s="15"/>
+    </row>
+    <row r="519" spans="31:31">
+      <c r="AE519" s="15"/>
+    </row>
+    <row r="520" spans="31:31">
+      <c r="AE520" s="15"/>
+    </row>
+    <row r="521" spans="31:31">
+      <c r="AE521" s="15"/>
+    </row>
+    <row r="522" spans="31:31">
+      <c r="AE522" s="15"/>
+    </row>
+    <row r="523" spans="31:31">
+      <c r="AE523" s="15"/>
+    </row>
+    <row r="524" spans="31:31">
+      <c r="AE524" s="15"/>
+    </row>
+    <row r="525" spans="31:31">
+      <c r="AE525" s="15"/>
+    </row>
+    <row r="526" spans="31:31">
+      <c r="AE526" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="J1:R1"/>
     <mergeCell ref="S1:Y1"/>
-    <mergeCell ref="Z1:AK1"/>
-    <mergeCell ref="AL1:AN1"/>
+    <mergeCell ref="Z1:AL1"/>
+    <mergeCell ref="AM1:AO1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G4" r:id="rId1" display="xxx@bankbjb.co.id"/>
+    <hyperlink ref="G4" r:id="rId1" display="xxxxxxx@bankbjb.co.id" tooltip="mailto:xxxxxxx@bankbjb.co.id"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
